--- a/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
+++ b/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
@@ -1785,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>729000000</v>
+        <v>-600000000</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 CNTT -&gt; VT</t>
+          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TP.HCM TNHH</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>Nhập VTTB điều động theo VB:3681/EVNHCM-VTCNTT+KH+KT+TCKT ngày 20/07/2026, PGH:03.VA4.40.0070</t>
+          <t>Đchỉnh TK 336314 qua TK 336358 R0726ST014+ST015/31.07.26</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -2306,11 +2306,11 @@
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-600000000</v>
+        <v>-1328275636</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TP.HCM TNHH</t>
+          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TPHCM TNHH</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="E20" s="16" t="n">
-        <v>-1328275636</v>
+        <v>-2000000000</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TPHCM TNHH</t>
+          <t>Nhận tiền tạm nộp PCVT</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>Đchỉnh TK 336314 qua TK 336358 R0726ST014+ST015/31.07.26</t>
+          <t>PC Vũng Tàu chuyển tiền SXKD về Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>-2000000000</v>
+        <v>1963917778</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>Nhận tiền tạm nộp PCVT</t>
+          <t>Bảo hiểm T07/2026 TT2595-03/7/2026 BP + Bảo hiểm T07/2026 TT2595-03/7/2026 SG + Bảo hiểm T07/2026 TT2595-03/7/2026 TD + Bảo hiểm T07/2026 TT2595-03/7/2026 APD + Bảo hiểm T07/2026 TT2595-03/7/2026 DDO + Bảo hiểm T07/2026 TT2595-03/7/2026 CC + Bảo hiểm T07/2026 TT2595-03/7/2026 CNTT + Bảo hiểm T07/2026 TT2595-03/7/2026 LDCT + Bảo hiểm T07/2026 TT2595-03/7/2026 TND + Bảo hiểm T07/2026 TT2595-03/7/2026 CL + Bảo hiểm T07/2026 TT2595-03/7/2026 BC + Bảo hiểm T07/2026 TT2595-03/7/2026 BD + Bảo hiểm T07/2026 TT2595-03/7/2026 HM + Bảo hiểm T07/2026 TT2595-03/7/2026 KH + Bảo hiểm T07/2026 TT2595-03/7/2026 BCA + Bảo hiểm T07/2026 TT2595-03/7/2026 DVDL + Bảo hiểm T07/2026 TT2595-03/7/2026 TA + Bảo hiểm T07/2026 TT2595-03/7/2026 DD + Bảo hiểm T07/2026 TT2595-03/7/2026 VT + Bảo hiểm T07/2026 TT2595-03/7/2026 GD + Bảo hiểm T07/2026 TT2595-03/7/2026 TT</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>PC Vũng Tàu chuyển tiền SXKD về Tổng công ty</t>
+          <t>Nhập tiền cấp bảo hiểm T7/26 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>1963917778</v>
+        <v>3951311154</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Bảo hiểm T07/2026 TT2595-03/7/2026 BP + Bảo hiểm T07/2026 TT2595-03/7/2026 SG + Bảo hiểm T07/2026 TT2595-03/7/2026 TD + Bảo hiểm T07/2026 TT2595-03/7/2026 APD + Bảo hiểm T07/2026 TT2595-03/7/2026 DDO + Bảo hiểm T07/2026 TT2595-03/7/2026 CC + Bảo hiểm T07/2026 TT2595-03/7/2026 CNTT + Bảo hiểm T07/2026 TT2595-03/7/2026 LDCT + Bảo hiểm T07/2026 TT2595-03/7/2026 TND + Bảo hiểm T07/2026 TT2595-03/7/2026 CL + Bảo hiểm T07/2026 TT2595-03/7/2026 BC + Bảo hiểm T07/2026 TT2595-03/7/2026 BD + Bảo hiểm T07/2026 TT2595-03/7/2026 HM + Bảo hiểm T07/2026 TT2595-03/7/2026 KH + Bảo hiểm T07/2026 TT2595-03/7/2026 BCA + Bảo hiểm T07/2026 TT2595-03/7/2026 DVDL + Bảo hiểm T07/2026 TT2595-03/7/2026 TA + Bảo hiểm T07/2026 TT2595-03/7/2026 DD + Bảo hiểm T07/2026 TT2595-03/7/2026 VT + Bảo hiểm T07/2026 TT2595-03/7/2026 GD + Bảo hiểm T07/2026 TT2595-03/7/2026 TT</t>
+          <t>Lương bs Quý 2/2026 đợt 1 BC + Lương bs Quý 2/2026 đợt 1 CL + Lương bs Quý 2/2026 đợt 1 GD + Lương bs Quý 2/2026 đợt 1 LDCT + Lương bs Quý 2/2026 đợt 1 DVDL + Lương bs Quý 2/2026 đợt 1 APD + Lương bs Quý 2/2026 đợt 1 SG + Lương bs Quý 2/2026 đợt 1 BD + Lương bs Quý 2/2026 đợt 1 BP + Lương bs Quý 2/2026 đợt 1 CC + Lương bs Quý 2/2026 đợt 1 TND + Lương bs Quý 2/2026 đợt 1 KH + Lương bs Quý 2/2026 đợt 1 CNTT + Lương bs Quý 2/2026 đợt 1 DD + Lương bs Quý 2/2026 đợt 1 TD + Lương bs Quý 2/2026 đợt 1 VT + Lương bs Quý 2/2026 đợt 1 TA + Lương bs Quý 2/2026 đợt 1 DDO + Lương bs Quý 2/2026 đợt 1 HM + Lương bs Quý 2/2026 đợt 1 BCA + Lương bs Quý 2/2026 đợt 1 TT</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền cấp bảo hiểm T7/26 từ Tổng công ty</t>
+          <t>Điều chỉnh hạch toán TK1131 theo G0726SC0110-10/7/26 cấp tiền lương bổ sung Q2/26 đợt 1 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>3951311154</v>
+        <v>6973534340</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>Lương bs Quý 2/2026 đợt 1 BC + Lương bs Quý 2/2026 đợt 1 CL + Lương bs Quý 2/2026 đợt 1 GD + Lương bs Quý 2/2026 đợt 1 LDCT + Lương bs Quý 2/2026 đợt 1 DVDL + Lương bs Quý 2/2026 đợt 1 APD + Lương bs Quý 2/2026 đợt 1 SG + Lương bs Quý 2/2026 đợt 1 BD + Lương bs Quý 2/2026 đợt 1 BP + Lương bs Quý 2/2026 đợt 1 CC + Lương bs Quý 2/2026 đợt 1 TND + Lương bs Quý 2/2026 đợt 1 KH + Lương bs Quý 2/2026 đợt 1 CNTT + Lương bs Quý 2/2026 đợt 1 DD + Lương bs Quý 2/2026 đợt 1 TD + Lương bs Quý 2/2026 đợt 1 VT + Lương bs Quý 2/2026 đợt 1 TA + Lương bs Quý 2/2026 đợt 1 DDO + Lương bs Quý 2/2026 đợt 1 HM + Lương bs Quý 2/2026 đợt 1 BCA + Lương bs Quý 2/2026 đợt 1 TT</t>
+          <t>Cấp ĐMT T05/2026 d2 TT2248-17/6/2026</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Điều chỉnh hạch toán TK1131 theo G0726SC0110-10/7/26 cấp tiền lương bổ sung Q2/26 đợt 1 từ Tổng công ty</t>
+          <t xml:space="preserve">Nhập tiền Tổng công ty HCM cấp tiền thanh toán Điện MTMN T05-2026 Đợt 2 </t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2471,16 +2471,16 @@
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>6973534340</v>
+        <v>3451399200</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Cấp ĐMT T05/2026 d2 TT2248-17/6/2026</t>
+          <t>Lương kỳ 1 T07/2026 LDCT + Lương kỳ 1 T07/2026 DVDL + Lương kỳ 1 T07/2026 KH + Lương kỳ 1 T07/2026 SG + Lương kỳ 1 T07/2026 CC + Lương kỳ 1 T07/2026 BC + Lương kỳ 1 T07/2026 TND + Lương kỳ 1 T07/2026 CNTT + Lương kỳ 1 T07/2026 BP + Lương kỳ 1 T07/2026 HM + Lương kỳ 1 T07/2026 DDO + Lương kỳ 1 T07/2026 APD + Lương kỳ 1 T07/2026 CL + Lương kỳ 1 T07/2026 TT + Lương kỳ 1 T07/2026 BCA + Lương kỳ 1 T07/2026 VT + Lương kỳ 1 T07/2026 DD + Lương kỳ 1 T07/2026 BD + Lương kỳ 1 T07/2026 TD + Lương kỳ 1 T07/2026 TA + Lương kỳ 1 T07/2026 GD</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhập tiền Tổng công ty HCM cấp tiền thanh toán Điện MTMN T05-2026 Đợt 2 </t>
+          <t>Nhập tiền cấp lương kỳ 1 T7/26 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -2504,16 +2504,16 @@
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>3451399200</v>
+        <v>18062167524</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Lương kỳ 1 T07/2026 LDCT + Lương kỳ 1 T07/2026 DVDL + Lương kỳ 1 T07/2026 KH + Lương kỳ 1 T07/2026 SG + Lương kỳ 1 T07/2026 CC + Lương kỳ 1 T07/2026 BC + Lương kỳ 1 T07/2026 TND + Lương kỳ 1 T07/2026 CNTT + Lương kỳ 1 T07/2026 BP + Lương kỳ 1 T07/2026 HM + Lương kỳ 1 T07/2026 DDO + Lương kỳ 1 T07/2026 APD + Lương kỳ 1 T07/2026 CL + Lương kỳ 1 T07/2026 TT + Lương kỳ 1 T07/2026 BCA + Lương kỳ 1 T07/2026 VT + Lương kỳ 1 T07/2026 DD + Lương kỳ 1 T07/2026 BD + Lương kỳ 1 T07/2026 TD + Lương kỳ 1 T07/2026 TA + Lương kỳ 1 T07/2026 GD</t>
+          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền cấp lương kỳ 1 T7/26 từ Tổng công ty</t>
+          <t>Nhập tiền Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2537,16 +2537,16 @@
         </is>
       </c>
       <c r="E26" s="16" t="n">
-        <v>18062167524</v>
+        <v>3589537560</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
+          <t>Lương kỳ 2 T07/2026 GD + Lương kỳ 2 T07/2026 BC + Lương kỳ 2 T07/2026 HM + Lương kỳ 2 T07/2026 CC + Lương kỳ 2 T07/2026 VT + Lương kỳ 2 T07/2026 DDO + Lương kỳ 2 T07/2026 DVDL + Lương kỳ 2 T07/2026 BP + Lương kỳ 2 T07/2026 LDCT + Lương kỳ 2 T07/2026 SG + Lương kỳ 2 T07/2026 BD + Lương kỳ 2 T07/2026 TA + Lương kỳ 2 T07/2026 DD + Lương kỳ 2 T07/2026 TT + Lương kỳ 2 T07/2026 TD + Lương kỳ 2 T07/2026 CNTT + Lương kỳ 2 T07/2026 APD + Lương kỳ 2 T07/2026 BCA + Lương kỳ 2 T07/2026 KH + Lương kỳ 2 T07/2026 CL + Lương kỳ 2 T07/2026 TND</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
+          <t>Nhập tiền cấp lương kỳ 2 T7/26 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -2570,16 +2570,16 @@
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>3589537560</v>
+        <v>-100891088370</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>Lương kỳ 2 T07/2026 GD + Lương kỳ 2 T07/2026 BC + Lương kỳ 2 T07/2026 HM + Lương kỳ 2 T07/2026 CC + Lương kỳ 2 T07/2026 VT + Lương kỳ 2 T07/2026 DDO + Lương kỳ 2 T07/2026 DVDL + Lương kỳ 2 T07/2026 BP + Lương kỳ 2 T07/2026 LDCT + Lương kỳ 2 T07/2026 SG + Lương kỳ 2 T07/2026 BD + Lương kỳ 2 T07/2026 TA + Lương kỳ 2 T07/2026 DD + Lương kỳ 2 T07/2026 TT + Lương kỳ 2 T07/2026 TD + Lương kỳ 2 T07/2026 CNTT + Lương kỳ 2 T07/2026 APD + Lương kỳ 2 T07/2026 BCA + Lương kỳ 2 T07/2026 KH + Lương kỳ 2 T07/2026 CL + Lương kỳ 2 T07/2026 TND</t>
+          <t>_KC thuế bù trừ thuế GTGT điện tháng 6.2026 với thuế GTGT ra</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền cấp lương kỳ 2 T7/26 từ Tổng công ty</t>
+          <t>HT bù trừ tiền thuế GTGT T06/2026</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2603,16 +2603,16 @@
         </is>
       </c>
       <c r="E28" s="16" t="n">
-        <v>-100891088370</v>
+        <v>47879803</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>_KC thuế bù trừ thuế GTGT điện tháng 6.2026 với thuế GTGT ra</t>
+          <t>Cấp vốn SXKD (lãi vay) theo TTr 2676/TCKT ngày 09/7/26</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>HT bù trừ tiền thuế GTGT T06/2026</t>
+          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay Agribank</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -2636,16 +2636,16 @@
         </is>
       </c>
       <c r="E29" s="16" t="n">
-        <v>47879803</v>
+        <v>6277098679</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>Cấp vốn SXKD (lãi vay) theo TTr 2676/TCKT ngày 09/7/26</t>
+          <t>Cấp vốn SXKD thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán nợ gốc theo TTr 2839/TCKT ngày 16/7/26</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay Agribank</t>
+          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay SXKD</t>
         </is>
       </c>
     </row>
@@ -2660,25 +2660,25 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363611</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363611</t>
         </is>
       </c>
       <c r="E30" s="16" t="n">
-        <v>6277098679</v>
+        <v>1937832476</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Cấp vốn SXKD thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán nợ gốc theo TTr 2839/TCKT ngày 16/7/26</t>
+          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay SXKD</t>
+          <t>Nhập tiền thuế GTGT Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -2702,16 +2702,16 @@
         </is>
       </c>
       <c r="E31" s="16" t="n">
-        <v>1937832476</v>
+        <v>-2076322697</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
+          <t>KC thuế GTGT cấp tạm ứng T6.2026 sang công nợ thuế GTGT điện</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền thuế GTGT Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
+          <t>Kết chuyển tiền thuế GTGT Điện NLMT T05-2026</t>
         </is>
       </c>
     </row>
@@ -2721,30 +2721,30 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>1363611</t>
+          <t>1363613</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>3363611</t>
+          <t>3363613</t>
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>-2076322697</v>
+        <v>22176000</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>KC thuế GTGT cấp tạm ứng T6.2026 sang công nợ thuế GTGT điện</t>
+          <t>Cấp KHCB theo TTr 2418/TCKT ngày 24/6/2026 + Cấp thuế GTGT theo TTr 2418/TCKT ngày 24/6/2026</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển tiền thuế GTGT Điện NLMT T05-2026</t>
+          <t>Hạch toán thông báo số 4169/EVNHCMC ngày 29/7/26 cấp vốn KHCB thanh toán VAT CP vận chuyển cáp CT25038</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -2768,16 +2768,16 @@
         </is>
       </c>
       <c r="E33" s="16" t="n">
-        <v>22176000</v>
+        <v>7392000</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>Cấp KHCB theo TTr 2418/TCKT ngày 24/6/2026 + Cấp thuế GTGT theo TTr 2418/TCKT ngày 24/6/2026</t>
+          <t>Cấp thuế GTGT theo TTr 2796/TCKT ngày 14/7/2026 + Cấp KHCB theo TTr 2796/TCKT ngày 14/7/2026</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo số 4169/EVNHCMC ngày 29/7/26 cấp vốn KHCB thanh toán VAT CP vận chuyển cáp CT25038</t>
+          <t>Hạch toán thông báo 4087/25.07.26 cấp vốn KHCB thanh toán VAT hóa đơn 6602/24.06.26 CP vận chuyển cáp CT25038</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="E34" s="16" t="n">
-        <v>7392000</v>
+        <v>849600</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>Cấp thuế GTGT theo TTr 2796/TCKT ngày 14/7/2026 + Cấp KHCB theo TTr 2796/TCKT ngày 14/7/2026</t>
+          <t>Cấp thuế GTGT theo TTr 2923/TCKT ngày 22/7/26 + Cấp KHCB theo TTr 2923/TCKT ngày 22/7/26</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo 4087/25.07.26 cấp vốn KHCB thanh toán VAT hóa đơn 6602/24.06.26 CP vận chuyển cáp CT25038</t>
+          <t>Hạch toán thông báo 4089/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB thanh toán VAT HĐ 187/23.06.26 PC Bến Cát  điều chuyển VTTB cho CT25039</t>
         </is>
       </c>
     </row>
@@ -2820,30 +2820,30 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>1363613</t>
+          <t>13638221</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>3363613</t>
+          <t>33638221</t>
         </is>
       </c>
       <c r="E35" s="16" t="n">
-        <v>849600</v>
+        <v>5650687</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>Cấp thuế GTGT theo TTr 2923/TCKT ngày 22/7/26 + Cấp KHCB theo TTr 2923/TCKT ngày 22/7/26</t>
+          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo 4089/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB thanh toán VAT HĐ 187/23.06.26 PC Bến Cát  điều chuyển VTTB cho CT25039</t>
+          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Vi phạm HĐ điện</t>
         </is>
       </c>
     </row>
@@ -2858,16 +2858,16 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>13638221</t>
+          <t>1363843</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>33638221</t>
+          <t>3363843</t>
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>5650687</v>
+        <v>12789477</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Vi phạm HĐ điện</t>
+          <t>Kết chuyển lợi nhuận hoạt động SXK, KD khác tháng 07/2026</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>1363843</t>
+          <t>1363847</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>3363843</t>
+          <t>3363847</t>
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>12789477</v>
+        <v>6574975</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận hoạt động SXK, KD khác tháng 07/2026</t>
+          <t>Kết chuyển lợi nhuận hoạt động tài chính tháng 07/2026</t>
         </is>
       </c>
     </row>
@@ -2924,16 +2924,16 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>1363847</t>
+          <t>1363848</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>3363847</t>
+          <t>3363848</t>
         </is>
       </c>
       <c r="E38" s="16" t="n">
-        <v>6574975</v>
+        <v>-2514378</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận hoạt động tài chính tháng 07/2026</t>
+          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - KHTSCĐ</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-2514378</v>
+        <v>31649</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - KHTSCĐ</t>
+          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Thu dư, thu khác</t>
         </is>
       </c>
     </row>
@@ -2985,30 +2985,30 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>1363848</t>
+          <t>1363888</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>3363848</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="E40" s="16" t="n">
-        <v>31649</v>
+        <v>-9455518323</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
+          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 1853 cuả UBND Phường Phú Mỹ</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Thu dư, thu khác</t>
+          <t>PCVT chuyển tiền công trình"Mở rộng, di dời lưới điện THT đường PMỹ-Tóc Tiên khu TĐC 105Ha đến đường Hắc Dịch-Tóc Tiên, Châu Pha (Quyết định 1853/QĐ-UBND ngày 29/06/26)"</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -3032,103 +3032,113 @@
         </is>
       </c>
       <c r="E41" s="16" t="n">
-        <v>-9455518323</v>
+        <v>-365738924</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 1853 cuả UBND Phường Phú Mỹ</t>
+          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 2829-17/7/2026 của UBND Phường Phú Mỹ</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>PCVT chuyển tiền công trình"Mở rộng, di dời lưới điện THT đường PMỹ-Tóc Tiên khu TĐC 105Ha đến đường Hắc Dịch-Tóc Tiên, Châu Pha (Quyết định 1853/QĐ-UBND ngày 29/06/26)"</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>1363888</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>33688</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>-365738924</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 2829-17/7/2026 của UBND Phường Phú Mỹ</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
           <t>Chuyển tiền về TCT công trình"DD hệ thống lưới điện trung, hạ thế thuộc dự án đường quy hoạch D22 KDC 3B đô thị mới PMỹ" (Quyết định 2829/17.07.26)</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>2. DANH SÁCH BÚT TOÁN KHUYẾT BỊ LỆCH THEO TỪNG CẶP TÀI KHOẢN</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>2. DANH SÁCH BÚT TOÁN KHUYẾT BỊ LỆCH THEO TỪNG CẶP TÀI KHOẢN</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TK HCM</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>TK PCVT</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Số Tiền Lệch Cặp</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Đơn Vị Khuyết</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Ngày CT</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Số CT GL</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Số Tiền Bút Toán</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Diễn Giải Bút Toán</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Người Lập</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>TK HCM</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>TK PCVT</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Số Tiền Lệch Cặp</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Đơn Vị Khuyết</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Ngày CT</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Số CT GL</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Số Tiền Bút Toán</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Diễn Giải Bút Toán</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Người Lập</t>
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>1363111</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>3363111</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>-1372690826013</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>2392</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>1370572291416</v>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>K/c 51111 &gt; 3363111 (k/c doanh thu điện)</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -3158,36 +3168,36 @@
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1370572291416</v>
+        <v>2118534597</v>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>K/c 51111 &gt; 3363111 (k/c doanh thu điện)</t>
+          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
+          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>1363111</t>
+          <t>1363112</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>3363111</t>
+          <t>3363112</t>
         </is>
       </c>
       <c r="C48" s="16" t="n">
-        <v>-1372690826013</v>
+        <v>-715006423</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
@@ -3201,40 +3211,40 @@
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="G48" s="18" t="n">
-        <v>2118534597</v>
+        <v>715006423</v>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
+          <t>K/c 51113 &gt; 3363112 (k/c dthu công suất phản kháng)</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
+          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>1363112</t>
+          <t>136314</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>3363112</t>
+          <t>336314</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>-715006423</v>
+        <v>-2400368334</v>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
@@ -3244,20 +3254,20 @@
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>715006423</v>
+        <v>-2146794974</v>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>K/c 51113 &gt; 3363112 (k/c dthu công suất phản kháng)</t>
+          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
+          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
         </is>
       </c>
     </row>
@@ -3277,7 +3287,7 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
@@ -3287,40 +3297,40 @@
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-2146794974</v>
+        <v>253573360</v>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
+          <t>K/c 5114 (QL dây, cáp) &gt; 3363114</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
+          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>136314</t>
+          <t>136331</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>336314</t>
+          <t>336331</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>-2400368334</v>
+        <v>12540094089</v>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
@@ -3330,20 +3340,20 @@
       </c>
       <c r="F51" s="15" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>253573360</v>
+        <v>49541007713</v>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>K/c 5114 (QL dây, cáp) &gt; 3363114</t>
+          <t>Trả gốc SPC từ T7 đến T12.2025 - Cac khoan vay thuoc BRVT</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
+          <t xml:space="preserve">DIEMHTK.HCM.NG </t>
         </is>
       </c>
     </row>
@@ -3363,7 +3373,7 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
@@ -3373,36 +3383,36 @@
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>49541007713</v>
+        <v>37000913624</v>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>Trả gốc SPC từ T7 đến T12.2025 - Cac khoan vay thuoc BRVT</t>
+          <t>Hạch toán món HCMC chuyển tiền cho SPC để hoàn trả tiền SPC vay</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIEMHTK.HCM.NG </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>136331</t>
+          <t>136351</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>336331</t>
+          <t>336351</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>12540094089</v>
+        <v>1747497667</v>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
@@ -3411,25 +3421,25 @@
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>37000913624</v>
+        <v>-290152778</v>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán món HCMC chuyển tiền cho SPC để hoàn trả tiền SPC vay</t>
+          <t>VTAD2608001_K/c CP SCL Công xa 7/2026</t>
         </is>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">TUAN2HM.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -3463,11 +3473,11 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>-290152778</v>
+        <v>-554412343</v>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>VTAD2608001_K/c CP SCL Công xa 7/2026</t>
+          <t>VTAD2606002_K/c CP SCL LBFCO,FCO,LA 7/2026</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
@@ -3497,20 +3507,20 @@
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>-554412343</v>
+        <v>-902932546</v>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>VTAD2606002_K/c CP SCL LBFCO,FCO,LA 7/2026</t>
+          <t>VTA2606001-SCL TU, TI Nam 2026-Dieu chinh CT2111-29.07.26</t>
         </is>
       </c>
       <c r="I55" s="15" t="inlineStr">
@@ -3522,20 +3532,20 @@
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>136352</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>336351</t>
+          <t>336352</t>
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>1747497667</v>
+        <v>15555384491</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
@@ -3545,20 +3555,20 @@
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="G56" s="18" t="n">
-        <v>-902932546</v>
+        <v>6501103895</v>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>VTA2606001-SCL TU, TI Nam 2026-Dieu chinh CT2111-29.07.26</t>
+          <t>K/c chi phí khấu hao đơn vị chuyển về TCT tháng 7/2026 - vốn Vay</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TUAN2HM.HCM.VTA </t>
+          <t xml:space="preserve">MINHDQ.HCM.NG </t>
         </is>
       </c>
     </row>
@@ -3592,11 +3602,11 @@
         </is>
       </c>
       <c r="G57" s="18" t="n">
-        <v>6501103895</v>
+        <v>9054280596</v>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>K/c chi phí khấu hao đơn vị chuyển về TCT tháng 7/2026 - vốn Vay</t>
+          <t>K/c chi phí khấu hao đơn vị chuyển về TCT tháng 7/2026 - vốn NS</t>
         </is>
       </c>
       <c r="I57" s="15" t="inlineStr">
@@ -3608,16 +3618,16 @@
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>136352</t>
+          <t>136358</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>336352</t>
+          <t>336358</t>
         </is>
       </c>
       <c r="C58" s="16" t="n">
-        <v>15555384491</v>
+        <v>1269718422875</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
@@ -3631,20 +3641,20 @@
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="G58" s="18" t="n">
-        <v>9054280596</v>
+        <v>1320517500</v>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>K/c chi phí khấu hao đơn vị chuyển về TCT tháng 7/2026 - vốn NS</t>
+          <t>VTDD T7/2026 TNĐL -&gt; VT</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINHDQ.HCM.NG </t>
+          <t xml:space="preserve">NAM7NH.HCM.NG </t>
         </is>
       </c>
     </row>
@@ -3674,15 +3684,15 @@
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1320517500</v>
+        <v>729000000</v>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 TNĐL -&gt; VT</t>
+          <t>VTDD T7/2026 CNTT -&gt; VT</t>
         </is>
       </c>
       <c r="I59" s="15" t="inlineStr">
@@ -3717,15 +3727,15 @@
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>-4274472878</v>
+        <v>1075800000</v>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 VT (SXKD)</t>
+          <t>VTDD T7/2026 DVĐL -&gt; VT</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
@@ -3750,7 +3760,7 @@
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
@@ -3760,20 +3770,20 @@
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-44500540533</v>
+        <v>-4274472878</v>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển công nợ nội bộ tháng 07/2026</t>
+          <t>VTDD T7/2026 VT (SXKD)</t>
         </is>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
+          <t xml:space="preserve">NAM7NH.HCM.NG </t>
         </is>
       </c>
     </row>
@@ -3803,20 +3813,20 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-2180703957</v>
+        <v>-44500540533</v>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển TK635111 về TCT qua TK công nợ 336358 tháng 7/2026</t>
+          <t>Kết chuyển công nợ nội bộ tháng 07/2026</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -3846,15 +3856,15 @@
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>12540094089</v>
+        <v>-2180703957</v>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán món HCMC chuyển tiền cho SPC để hoàn trả tiền SPC vay</t>
+          <t>Kết chuyển TK635111 về TCT qua TK công nợ 336358 tháng 7/2026</t>
         </is>
       </c>
       <c r="I63" s="15" t="inlineStr">
@@ -3884,25 +3894,25 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-198647000</v>
+        <v>12540094089</v>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>Xuất công tơ lên Cty Thí Nghiệm kiểm định</t>
+          <t>Hạch toán món HCMC chuyển tiền cho SPC để hoàn trả tiền SPC vay</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4142,41 +4152,41 @@
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>-282012</v>
+        <v>-1235577272474</v>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>HT bù trừ chi phí điện mua nội bộ trong tháng</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">TUAN2HM.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363611</t>
         </is>
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363611</t>
         </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2118534597</v>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
@@ -4185,41 +4195,41 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>-312162</v>
+        <v>-2118534597</v>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
         </is>
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363613</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363613</t>
         </is>
       </c>
       <c r="C72" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2366815</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
@@ -4228,84 +4238,84 @@
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-456000</v>
+        <v>-2366815</v>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Chuyển tiền thuế GTGT đã cấp về HCMC CT23009</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>136391</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>336391</t>
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2146794974</v>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>-476759</v>
+        <v>2146794974</v>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
         </is>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C74" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
@@ -4314,41 +4324,41 @@
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-541924</v>
+        <v>-265009971</v>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23009</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C75" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
@@ -4357,41 +4367,41 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-1063130</v>
+        <v>-178745132</v>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23018</t>
         </is>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C76" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
@@ -4400,41 +4410,41 @@
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-1107131</v>
+        <v>-312155008</v>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21002</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
@@ -4443,41 +4453,41 @@
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-1456000</v>
+        <v>-308130</v>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho ĐVTC đền tiền Vật tư A cấp - CT23009</t>
         </is>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C78" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
@@ -4486,41 +4496,41 @@
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-2171718</v>
+        <v>-603285984</v>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21017</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C79" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
@@ -4529,41 +4539,41 @@
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>-2239885</v>
+        <v>-1016165</v>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho, ĐVTC đền tiền Vật tư A cấp CT21002</t>
         </is>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C80" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
@@ -4572,41 +4582,41 @@
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>-2373897</v>
+        <v>-31039400</v>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23009</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C81" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
@@ -4615,41 +4625,41 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>-2405387</v>
+        <v>-48568000</v>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP thiết bị điều chuyển từ SXKD CT21002</t>
         </is>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C82" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
@@ -4658,41 +4668,41 @@
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>-3498676</v>
+        <v>-18000000</v>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23018</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C83" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
@@ -4701,41 +4711,41 @@
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>-3678470</v>
+        <v>-284000000</v>
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tiền VTTB điều chuyển từ SXKD qua các CT ĐTXD CT26004</t>
         </is>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C84" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
@@ -4744,41 +4754,41 @@
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>-4332900</v>
+        <v>-2415427234</v>
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán tiền VTTB điều chuyển từ SXKD qua các CT ĐTXD CT25006</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C85" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
@@ -4787,41 +4797,41 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>-7642834</v>
+        <v>-125371702</v>
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán chi phí CT22033</t>
         </is>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C86" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
@@ -4830,41 +4840,41 @@
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>-9733864</v>
+        <v>-289871682</v>
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán chi phí CT23007</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C87" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
@@ -4873,41 +4883,41 @@
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>-14691798</v>
+        <v>-275458537</v>
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán chi phí CT21007</t>
         </is>
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C88" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
@@ -4916,41 +4926,41 @@
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>-16461125</v>
+        <v>-848733059</v>
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán chi phí CT20009</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C89" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
@@ -4959,41 +4969,41 @@
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>-17483605</v>
+        <v>-240595694</v>
       </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán chi phí CT24006</t>
         </is>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C90" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
@@ -5002,41 +5012,41 @@
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>-18299769</v>
+        <v>-155287323</v>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>Thanh toán chi phí CT21055</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C91" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
@@ -5045,20 +5055,20 @@
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-19078116</v>
+        <v>292565243</v>
       </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
@@ -5070,16 +5080,16 @@
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C92" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
@@ -5088,20 +5098,20 @@
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>-24987945</v>
+        <v>-24025976</v>
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>25039-SX:Xuất Vtư từ Ctr Trang TBị đóng cắt Scada đ/c trả lại kho SXKD do cấp thừa</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -5113,16 +5123,16 @@
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C93" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
@@ -5131,20 +5141,20 @@
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>-29109060</v>
+        <v>14264000</v>
       </c>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I93" s="15" t="inlineStr">
@@ -5156,16 +5166,16 @@
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C94" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
@@ -5174,20 +5184,20 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>-32664248</v>
+        <v>119133842</v>
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SXKD-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -5199,16 +5209,16 @@
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C95" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
@@ -5217,20 +5227,20 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>-49234940</v>
+        <v>12303466</v>
       </c>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
         </is>
       </c>
       <c r="I95" s="15" t="inlineStr">
@@ -5242,16 +5252,16 @@
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C96" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
@@ -5260,20 +5270,20 @@
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>-51137926</v>
+        <v>-104673235</v>
       </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>25017-SX:Xuất Vtư thừa từ Ctr 25017-Lộ ra Côn Đảo điều chuyển SXKD phục vụ SCTX</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
@@ -5285,16 +5295,16 @@
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C97" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
@@ -5303,20 +5313,20 @@
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>-55644729</v>
+        <v>91276000</v>
       </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I97" s="15" t="inlineStr">
@@ -5328,16 +5338,16 @@
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C98" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
@@ -5346,20 +5356,20 @@
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>-90205369</v>
+        <v>41322000</v>
       </c>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển cho Ctr 25018-Tụ bù trung thế 2025</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
@@ -5371,16 +5381,16 @@
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C99" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
@@ -5389,20 +5399,20 @@
       </c>
       <c r="E99" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>-93781294</v>
+        <v>-267630000</v>
       </c>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>24027-SX:Xuất Vtư từ Ctr 24027- CQT Tx.Phú Mỹ để điều chuyển qua SXKD</t>
         </is>
       </c>
       <c r="I99" s="15" t="inlineStr">
@@ -5414,16 +5424,16 @@
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C100" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
@@ -5432,20 +5442,20 @@
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>-106800000</v>
+        <v>95719600</v>
       </c>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039- Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
@@ -5457,16 +5467,16 @@
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C101" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
@@ -5475,20 +5485,20 @@
       </c>
       <c r="E101" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>-120372075</v>
+        <v>51954506</v>
       </c>
       <c r="H101" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I101" s="15" t="inlineStr">
@@ -5500,16 +5510,16 @@
     <row r="102">
       <c r="A102" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C102" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
@@ -5518,20 +5528,20 @@
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-301812800</v>
+        <v>13378750</v>
       </c>
       <c r="H102" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
@@ -5543,16 +5553,16 @@
     <row r="103">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C103" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
@@ -5561,20 +5571,20 @@
       </c>
       <c r="E103" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>-902489702</v>
+        <v>-817800</v>
       </c>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>24029-SX:Xuất Vtư Ctr 24029-Lộ ra Tân Phước đ/chuyển SXKD phục vụ SCTX</t>
         </is>
       </c>
       <c r="I103" s="15" t="inlineStr">
@@ -5586,16 +5596,16 @@
     <row r="104">
       <c r="A104" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C104" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
@@ -5604,20 +5614,20 @@
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G104" s="18" t="n">
-        <v>-1010358200</v>
+        <v>12799411</v>
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Xuất vật tư bán thanh lý căn cứ Hợp đồng số 3501/2026/HĐ-EVNHCMC-NGUYETMINH2 ngày 01.07.2026</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển qua Ctr 25039- Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
@@ -5629,16 +5639,16 @@
     <row r="105">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C105" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D105" s="15" t="inlineStr">
         <is>
@@ -5647,41 +5657,41 @@
       </c>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>65</v>
+        <v>46285000</v>
       </c>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>Nhập kho điều động VTTB theo TBĐĐ: 3632  06/07/2026 và TBĐĐ:3791 10/07/2026</t>
+          <t>Xuất VTTB  03.VH1.51.0024 /15.06.26 về ĐTXD (Máy tính xách tay _Nguyễn Văn Quyến +Thước đo lăn+Thước đo bằng tia Laser cho P.QLĐT)</t>
         </is>
       </c>
       <c r="I105" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C106" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
@@ -5690,41 +5700,41 @@
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>33</v>
+        <v>7962963</v>
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Nhập kho điều động VTTB theo TBĐĐ: 3734+  3761+3760    08/07/2026</t>
+          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 440/21.07.26</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C107" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
@@ -5733,41 +5743,41 @@
       </c>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>202</v>
+        <v>8473850</v>
       </c>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>Nhập lại công tơ kiểm định không đạt theo PGH:03.UW2.57.3280</t>
+          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 600/29.07.26</t>
         </is>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C108" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
@@ -5776,2259 +5786,23 @@
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>438</v>
+        <v>4619000</v>
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>nHập lại công tơ msau khi kiểm định đạt theo PGH:03.UW2.57.3057</t>
+          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 2161/30.07.26</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C109" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E109" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F109" s="15" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G109" s="18" t="n">
-        <v>53</v>
-      </c>
-      <c r="H109" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại công tơ sau khi kiểm định không đạt theo PGH:03.UW2.57.3055+03.UW2.57.3059 (13/7/2026)+</t>
-        </is>
-      </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B110" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F110" s="15" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G110" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="H110" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại công tơ sau khi kiểm định không đạt theo PGH:03.UW2.57.3059 (13/7/2026)</t>
-        </is>
-      </c>
-      <c r="I110" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B111" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="F111" s="15" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="G111" s="18" t="n">
-        <v>34624096</v>
-      </c>
-      <c r="H111" s="17" t="inlineStr">
-        <is>
-          <t>NHập lại công tơ sau khi kiểm định theo PGH:03.UW2.57.2918</t>
-        </is>
-      </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B112" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="F112" s="15" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="G112" s="18" t="n">
-        <v>199382000</v>
-      </c>
-      <c r="H112" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại công tơ sau khi kiểm định theo PGH:03.UW2.57.3281</t>
-        </is>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B113" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C113" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E113" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F113" s="15" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G113" s="18" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H113" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại điện kế sau khi kiểm định theo PGH:03.UW2.57.3206+03.UW2.57.3205 -21/07/2026</t>
-        </is>
-      </c>
-      <c r="I113" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B114" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="F114" s="15" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="G114" s="18" t="n">
-        <v>1633642</v>
-      </c>
-      <c r="H114" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại TI  hạ thế kiểm định đạt theo PGH03.UW2.57.3310</t>
-        </is>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B115" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E115" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="F115" s="15" t="inlineStr">
-        <is>
-          <t>2149</t>
-        </is>
-      </c>
-      <c r="G115" s="18" t="n">
-        <v>9030318</v>
-      </c>
-      <c r="H115" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại TU, TI  trung hạ thế sau khi thử nghiệm theo PGH:03.UW2.57.2987</t>
-        </is>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B116" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="F116" s="15" t="inlineStr">
-        <is>
-          <t>2149</t>
-        </is>
-      </c>
-      <c r="G116" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="H116" s="17" t="inlineStr">
-        <is>
-          <t>Nhập lại  TI   hạ thế sau khi thử nghiệm theo PGH:03.UW2.57.2988</t>
-        </is>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B117" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E117" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="F117" s="15" t="inlineStr">
-        <is>
-          <t>2140</t>
-        </is>
-      </c>
-      <c r="G117" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H117" s="17" t="inlineStr">
-        <is>
-          <t>NHập lia5i TI TT kiểm định không đạt theo PGH:03.UW2.57.3194</t>
-        </is>
-      </c>
-      <c r="I117" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B118" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C118" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="F118" s="15" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="G118" s="18" t="n">
-        <v>103</v>
-      </c>
-      <c r="H118" s="17" t="inlineStr">
-        <is>
-          <t>Nhập theo TBĐĐ 3791/10.7.26 - khi kiểm định theo PGH:03.UW4.57.0001</t>
-        </is>
-      </c>
-      <c r="I118" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E119" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F119" s="15" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="G119" s="18" t="n">
-        <v>169</v>
-      </c>
-      <c r="H119" s="17" t="inlineStr">
-        <is>
-          <t>Nhập VTTB điều động theo TB số 3495 ngày 01/07/2026 và PGH:03.UW2.57.2919</t>
-        </is>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="G120" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="H120" s="17" t="inlineStr">
-        <is>
-          <t>Nhập VTTB điều động theo TB số 3545 ngày 02/07/2026 và PGH:03.UW2.57.2920</t>
-        </is>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D121" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E121" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F121" s="15" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G121" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="H121" s="17" t="inlineStr">
-        <is>
-          <t>Nhập VTTB điều động theo TB:3876+3877+3890-15/07/2026 PGH:03.UW4.57.0070+03.UW2.57.3166</t>
-        </is>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>136358</t>
-        </is>
-      </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="n">
-        <v>1269718422875</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F122" s="15" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="G122" s="18" t="n">
-        <v>-1235577272474</v>
-      </c>
-      <c r="H122" s="17" t="inlineStr">
-        <is>
-          <t>HT bù trừ chi phí điện mua nội bộ trong tháng</t>
-        </is>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TUAN2HM.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="inlineStr">
-        <is>
-          <t>1363611</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="inlineStr">
-        <is>
-          <t>3363611</t>
-        </is>
-      </c>
-      <c r="C123" s="16" t="n">
-        <v>2118534597</v>
-      </c>
-      <c r="D123" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E123" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F123" s="15" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="G123" s="18" t="n">
-        <v>-2118534597</v>
-      </c>
-      <c r="H123" s="17" t="inlineStr">
-        <is>
-          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
-        </is>
-      </c>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="15" t="inlineStr">
-        <is>
-          <t>1363613</t>
-        </is>
-      </c>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>3363613</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="n">
-        <v>2366815</v>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E124" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F124" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G124" s="18" t="n">
-        <v>-2366815</v>
-      </c>
-      <c r="H124" s="17" t="inlineStr">
-        <is>
-          <t>Chuyển tiền thuế GTGT đã cấp về HCMC CT23009</t>
-        </is>
-      </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="15" t="inlineStr">
-        <is>
-          <t>136391</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="inlineStr">
-        <is>
-          <t>336391</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="n">
-        <v>2146794974</v>
-      </c>
-      <c r="D125" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
-        </is>
-      </c>
-      <c r="E125" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F125" s="15" t="inlineStr">
-        <is>
-          <t>7745</t>
-        </is>
-      </c>
-      <c r="G125" s="18" t="n">
-        <v>2146794974</v>
-      </c>
-      <c r="H125" s="17" t="inlineStr">
-        <is>
-          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
-        </is>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B126" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F126" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G126" s="18" t="n">
-        <v>-265009971</v>
-      </c>
-      <c r="H126" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23009</t>
-        </is>
-      </c>
-      <c r="I126" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B127" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D127" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E127" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F127" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G127" s="18" t="n">
-        <v>-178745132</v>
-      </c>
-      <c r="H127" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23018</t>
-        </is>
-      </c>
-      <c r="I127" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B128" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D128" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F128" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G128" s="18" t="n">
-        <v>-312155008</v>
-      </c>
-      <c r="H128" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21002</t>
-        </is>
-      </c>
-      <c r="I128" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B129" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C129" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D129" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E129" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F129" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G129" s="18" t="n">
-        <v>-308130</v>
-      </c>
-      <c r="H129" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho ĐVTC đền tiền Vật tư A cấp - CT23009</t>
-        </is>
-      </c>
-      <c r="I129" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B130" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F130" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G130" s="18" t="n">
-        <v>-603285984</v>
-      </c>
-      <c r="H130" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21017</t>
-        </is>
-      </c>
-      <c r="I130" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B131" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D131" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E131" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F131" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G131" s="18" t="n">
-        <v>-1016165</v>
-      </c>
-      <c r="H131" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho, ĐVTC đền tiền Vật tư A cấp CT21002</t>
-        </is>
-      </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B132" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D132" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E132" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F132" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G132" s="18" t="n">
-        <v>-31039400</v>
-      </c>
-      <c r="H132" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23009</t>
-        </is>
-      </c>
-      <c r="I132" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B133" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C133" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D133" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E133" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F133" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G133" s="18" t="n">
-        <v>-48568000</v>
-      </c>
-      <c r="H133" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP thiết bị điều chuyển từ SXKD CT21002</t>
-        </is>
-      </c>
-      <c r="I133" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B134" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C134" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E134" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F134" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G134" s="18" t="n">
-        <v>-18000000</v>
-      </c>
-      <c r="H134" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23018</t>
-        </is>
-      </c>
-      <c r="I134" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B135" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C135" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D135" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E135" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F135" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G135" s="18" t="n">
-        <v>-284000000</v>
-      </c>
-      <c r="H135" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tiền VTTB điều chuyển từ SXKD qua các CT ĐTXD CT26004</t>
-        </is>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B136" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C136" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E136" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F136" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G136" s="18" t="n">
-        <v>-2415427234</v>
-      </c>
-      <c r="H136" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán tiền VTTB điều chuyển từ SXKD qua các CT ĐTXD CT25006</t>
-        </is>
-      </c>
-      <c r="I136" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B137" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C137" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D137" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E137" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F137" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G137" s="18" t="n">
-        <v>-125371702</v>
-      </c>
-      <c r="H137" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán chi phí CT22033</t>
-        </is>
-      </c>
-      <c r="I137" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B138" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C138" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E138" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F138" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G138" s="18" t="n">
-        <v>-289871682</v>
-      </c>
-      <c r="H138" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán chi phí CT23007</t>
-        </is>
-      </c>
-      <c r="I138" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B139" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C139" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D139" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E139" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F139" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G139" s="18" t="n">
-        <v>-275458537</v>
-      </c>
-      <c r="H139" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán chi phí CT21007</t>
-        </is>
-      </c>
-      <c r="I139" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B140" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C140" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E140" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F140" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G140" s="18" t="n">
-        <v>-848733059</v>
-      </c>
-      <c r="H140" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán chi phí CT20009</t>
-        </is>
-      </c>
-      <c r="I140" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C141" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D141" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E141" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F141" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G141" s="18" t="n">
-        <v>-240595694</v>
-      </c>
-      <c r="H141" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán chi phí CT24006</t>
-        </is>
-      </c>
-      <c r="I141" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B142" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C142" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E142" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F142" s="15" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="G142" s="18" t="n">
-        <v>-155287323</v>
-      </c>
-      <c r="H142" s="17" t="inlineStr">
-        <is>
-          <t>Thanh toán chi phí CT21055</t>
-        </is>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B143" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C143" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D143" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E143" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F143" s="15" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="G143" s="18" t="n">
-        <v>292565243</v>
-      </c>
-      <c r="H143" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I143" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B144" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C144" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E144" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F144" s="15" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="G144" s="18" t="n">
-        <v>-24025976</v>
-      </c>
-      <c r="H144" s="17" t="inlineStr">
-        <is>
-          <t>25039-SX:Xuất Vtư từ Ctr Trang TBị đóng cắt Scada đ/c trả lại kho SXKD do cấp thừa</t>
-        </is>
-      </c>
-      <c r="I144" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C145" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D145" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E145" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F145" s="15" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G145" s="18" t="n">
-        <v>14264000</v>
-      </c>
-      <c r="H145" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I145" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B146" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C146" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E146" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F146" s="15" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="G146" s="18" t="n">
-        <v>119133842</v>
-      </c>
-      <c r="H146" s="17" t="inlineStr">
-        <is>
-          <t>SXKD-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
-        </is>
-      </c>
-      <c r="I146" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D147" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E147" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="F147" s="15" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="G147" s="18" t="n">
-        <v>12303466</v>
-      </c>
-      <c r="H147" s="17" t="inlineStr">
-        <is>
-          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
-        </is>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B148" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C148" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E148" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F148" s="15" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="G148" s="18" t="n">
-        <v>-104673235</v>
-      </c>
-      <c r="H148" s="17" t="inlineStr">
-        <is>
-          <t>25017-SX:Xuất Vtư thừa từ Ctr 25017-Lộ ra Côn Đảo điều chuyển SXKD phục vụ SCTX</t>
-        </is>
-      </c>
-      <c r="I148" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B149" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C149" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D149" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E149" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="F149" s="15" t="inlineStr">
-        <is>
-          <t>2129</t>
-        </is>
-      </c>
-      <c r="G149" s="18" t="n">
-        <v>91276000</v>
-      </c>
-      <c r="H149" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I149" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B150" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C150" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E150" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F150" s="15" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G150" s="18" t="n">
-        <v>41322000</v>
-      </c>
-      <c r="H150" s="17" t="inlineStr">
-        <is>
-          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển cho Ctr 25018-Tụ bù trung thế 2025</t>
-        </is>
-      </c>
-      <c r="I150" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B151" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D151" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E151" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F151" s="15" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G151" s="18" t="n">
-        <v>-267630000</v>
-      </c>
-      <c r="H151" s="17" t="inlineStr">
-        <is>
-          <t>24027-SX:Xuất Vtư từ Ctr 24027- CQT Tx.Phú Mỹ để điều chuyển qua SXKD</t>
-        </is>
-      </c>
-      <c r="I151" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B152" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E152" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F152" s="15" t="inlineStr">
-        <is>
-          <t>2139</t>
-        </is>
-      </c>
-      <c r="G152" s="18" t="n">
-        <v>95719600</v>
-      </c>
-      <c r="H152" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039- Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I152" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C153" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D153" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E153" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F153" s="15" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="G153" s="18" t="n">
-        <v>51954506</v>
-      </c>
-      <c r="H153" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I153" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E154" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F154" s="15" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="G154" s="18" t="n">
-        <v>13378750</v>
-      </c>
-      <c r="H154" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I154" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D155" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E155" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F155" s="15" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="G155" s="18" t="n">
-        <v>-817800</v>
-      </c>
-      <c r="H155" s="17" t="inlineStr">
-        <is>
-          <t>24029-SX:Xuất Vtư Ctr 24029-Lộ ra Tân Phước đ/chuyển SXKD phục vụ SCTX</t>
-        </is>
-      </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B156" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C156" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E156" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="F156" s="15" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="G156" s="18" t="n">
-        <v>12799411</v>
-      </c>
-      <c r="H156" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển qua Ctr 25039- Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I156" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B157" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C157" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D157" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E157" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F157" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G157" s="18" t="n">
-        <v>46285000</v>
-      </c>
-      <c r="H157" s="17" t="inlineStr">
-        <is>
-          <t>Xuất VTTB  03.VH1.51.0024 /15.06.26 về ĐTXD (Máy tính xách tay _Nguyễn Văn Quyến +Thước đo lăn+Thước đo bằng tia Laser cho P.QLĐT)</t>
-        </is>
-      </c>
-      <c r="I157" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B158" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C158" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E158" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F158" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G158" s="18" t="n">
-        <v>7962963</v>
-      </c>
-      <c r="H158" s="17" t="inlineStr">
-        <is>
-          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 440/21.07.26</t>
-        </is>
-      </c>
-      <c r="I158" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B159" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D159" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E159" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F159" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G159" s="18" t="n">
-        <v>8473850</v>
-      </c>
-      <c r="H159" s="17" t="inlineStr">
-        <is>
-          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 600/29.07.26</t>
-        </is>
-      </c>
-      <c r="I159" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B160" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C160" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E160" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F160" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G160" s="18" t="n">
-        <v>4619000</v>
-      </c>
-      <c r="H160" s="17" t="inlineStr">
-        <is>
-          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 2161/30.07.26</t>
-        </is>
-      </c>
-      <c r="I160" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>

--- a/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
+++ b/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
@@ -1785,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>1363111</t>
+          <t>1363112</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>3363111</t>
+          <t>3363112</t>
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>86064000</v>
+        <v>56850487</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>KC thuế GTGT điều động tháng 7/2026 sang công nợ thuế GTGT điện</t>
+          <t>_KC thuế bù trừ thuế GTGT điện tháng 6.2026 với thuế GTGT ra</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>KC Thuế GTGT VTĐĐ- hđơn 941-06.07.26-TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>HT bù trừ tiền thuế GTGT T05/2026</t>
         </is>
       </c>
     </row>
@@ -2061,30 +2061,30 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>1363112</t>
+          <t>136314</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>3363112</t>
+          <t>336314</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>56850487</v>
+        <v>-973923044</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>_KC thuế bù trừ thuế GTGT điện tháng 6.2026 với thuế GTGT ra</t>
+          <t>Nhận tiền thuê cột điện PCVT</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>HT bù trừ tiền thuế GTGT T05/2026</t>
+          <t>SACOM_CNBRVT_CTY_DAYTT_841009</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -2108,11 +2108,11 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-973923044</v>
+        <v>-371540670</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>Nhận tiền thuê cột điện PCVT</t>
+          <t>PCVT chuyển tiền thuê cột điện</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -2127,30 +2127,30 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>136314</t>
+          <t>136341</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>336314</t>
+          <t>336341</t>
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-371540670</v>
+        <v>-6501103895</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>PCVT chuyển tiền thuê cột điện</t>
+          <t>K/c chi phí khấu hao đơn vị chuyển về TCT tháng 7/2026 - vốn Vay</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>SACOM_CNBRVT_CTY_DAYTT_841009</t>
+          <t>Kết chuyển chi phí khấu hao tháng 07/2026</t>
         </is>
       </c>
     </row>
@@ -2160,30 +2160,30 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>136331</t>
+          <t>136358</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>336331</t>
+          <t>336358</t>
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>10620000</v>
+        <v>1334423454272</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>Cấp thuế GTGT theo TTr 2923/TCKT ngày 22/7/26 + Cấp KHCB theo TTr 2923/TCKT ngày 22/7/26</t>
+          <t>Bán điện nội bộ</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo 4089/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB thanh toán HĐ 187/23.06.26 PC Bến Cát  điều chuyển VTTB cho CT25039</t>
+          <t>HT CP điện mua nội bộ T7/2026 (HĐ 1104_06/08/2026)</t>
         </is>
       </c>
     </row>
@@ -2193,30 +2193,30 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>136341</t>
+          <t>136358</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>336341</t>
+          <t>336358</t>
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-6501103895</v>
+        <v>-600000000</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>K/c chi phí khấu hao đơn vị chuyển về TCT tháng 7/2026 - vốn Vay</t>
+          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TP.HCM TNHH</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển chi phí khấu hao tháng 07/2026</t>
+          <t>Đchỉnh TK 336314 qua TK 336358 R0726ST014+ST015/31.07.26</t>
         </is>
       </c>
     </row>
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>1334423454272</v>
+        <v>-1328275636</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>Bán điện nội bộ</t>
+          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TPHCM TNHH</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>HT CP điện mua nội bộ T7/2026 (HĐ 1104_06/08/2026)</t>
+          <t>Đchỉnh TK 336314 qua TK 336358 R0726ST014+ST015/31.07.26</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-600000000</v>
+        <v>-2000000000</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TP.HCM TNHH</t>
+          <t>Nhận tiền tạm nộp PCVT</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>Đchỉnh TK 336314 qua TK 336358 R0726ST014+ST015/31.07.26</t>
+          <t>PC Vũng Tàu chuyển tiền SXKD về Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -2306,16 +2306,16 @@
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-1328275636</v>
+        <v>1963917778</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>CN TONG CONG TY DIEN LUC TP HCM TNHH - CTY DIEN LUC VUNG TAU PCVT CHUYEN TIEN QUYET TOAN NHAN CONG SXK NAM 2025 CV 2936/EVNHCMC- TCKT N12/06/26 TONG CONG TY DIEN LUC TPHCM TNHH</t>
+          <t>Bảo hiểm T07/2026 TT2595-03/7/2026 BP + Bảo hiểm T07/2026 TT2595-03/7/2026 SG + Bảo hiểm T07/2026 TT2595-03/7/2026 TD + Bảo hiểm T07/2026 TT2595-03/7/2026 APD + Bảo hiểm T07/2026 TT2595-03/7/2026 DDO + Bảo hiểm T07/2026 TT2595-03/7/2026 CC + Bảo hiểm T07/2026 TT2595-03/7/2026 CNTT + Bảo hiểm T07/2026 TT2595-03/7/2026 LDCT + Bảo hiểm T07/2026 TT2595-03/7/2026 TND + Bảo hiểm T07/2026 TT2595-03/7/2026 CL + Bảo hiểm T07/2026 TT2595-03/7/2026 BC + Bảo hiểm T07/2026 TT2595-03/7/2026 BD + Bảo hiểm T07/2026 TT2595-03/7/2026 HM + Bảo hiểm T07/2026 TT2595-03/7/2026 KH + Bảo hiểm T07/2026 TT2595-03/7/2026 BCA + Bảo hiểm T07/2026 TT2595-03/7/2026 DVDL + Bảo hiểm T07/2026 TT2595-03/7/2026 TA + Bảo hiểm T07/2026 TT2595-03/7/2026 DD + Bảo hiểm T07/2026 TT2595-03/7/2026 VT + Bảo hiểm T07/2026 TT2595-03/7/2026 GD + Bảo hiểm T07/2026 TT2595-03/7/2026 TT</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>Đchỉnh TK 336314 qua TK 336358 R0726ST014+ST015/31.07.26</t>
+          <t>Nhập tiền cấp bảo hiểm T7/26 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="E20" s="16" t="n">
-        <v>-2000000000</v>
+        <v>3951311154</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>Nhận tiền tạm nộp PCVT</t>
+          <t>Lương bs Quý 2/2026 đợt 1 BC + Lương bs Quý 2/2026 đợt 1 CL + Lương bs Quý 2/2026 đợt 1 GD + Lương bs Quý 2/2026 đợt 1 LDCT + Lương bs Quý 2/2026 đợt 1 DVDL + Lương bs Quý 2/2026 đợt 1 APD + Lương bs Quý 2/2026 đợt 1 SG + Lương bs Quý 2/2026 đợt 1 BD + Lương bs Quý 2/2026 đợt 1 BP + Lương bs Quý 2/2026 đợt 1 CC + Lương bs Quý 2/2026 đợt 1 TND + Lương bs Quý 2/2026 đợt 1 KH + Lương bs Quý 2/2026 đợt 1 CNTT + Lương bs Quý 2/2026 đợt 1 DD + Lương bs Quý 2/2026 đợt 1 TD + Lương bs Quý 2/2026 đợt 1 VT + Lương bs Quý 2/2026 đợt 1 TA + Lương bs Quý 2/2026 đợt 1 DDO + Lương bs Quý 2/2026 đợt 1 HM + Lương bs Quý 2/2026 đợt 1 BCA + Lương bs Quý 2/2026 đợt 1 TT</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>PC Vũng Tàu chuyển tiền SXKD về Tổng công ty</t>
+          <t>Điều chỉnh hạch toán TK1131 theo G0726SC0110-10/7/26 cấp tiền lương bổ sung Q2/26 đợt 1 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>1963917778</v>
+        <v>6973534340</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>Bảo hiểm T07/2026 TT2595-03/7/2026 BP + Bảo hiểm T07/2026 TT2595-03/7/2026 SG + Bảo hiểm T07/2026 TT2595-03/7/2026 TD + Bảo hiểm T07/2026 TT2595-03/7/2026 APD + Bảo hiểm T07/2026 TT2595-03/7/2026 DDO + Bảo hiểm T07/2026 TT2595-03/7/2026 CC + Bảo hiểm T07/2026 TT2595-03/7/2026 CNTT + Bảo hiểm T07/2026 TT2595-03/7/2026 LDCT + Bảo hiểm T07/2026 TT2595-03/7/2026 TND + Bảo hiểm T07/2026 TT2595-03/7/2026 CL + Bảo hiểm T07/2026 TT2595-03/7/2026 BC + Bảo hiểm T07/2026 TT2595-03/7/2026 BD + Bảo hiểm T07/2026 TT2595-03/7/2026 HM + Bảo hiểm T07/2026 TT2595-03/7/2026 KH + Bảo hiểm T07/2026 TT2595-03/7/2026 BCA + Bảo hiểm T07/2026 TT2595-03/7/2026 DVDL + Bảo hiểm T07/2026 TT2595-03/7/2026 TA + Bảo hiểm T07/2026 TT2595-03/7/2026 DD + Bảo hiểm T07/2026 TT2595-03/7/2026 VT + Bảo hiểm T07/2026 TT2595-03/7/2026 GD + Bảo hiểm T07/2026 TT2595-03/7/2026 TT</t>
+          <t>Cấp ĐMT T05/2026 d2 TT2248-17/6/2026</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền cấp bảo hiểm T7/26 từ Tổng công ty</t>
+          <t xml:space="preserve">Nhập tiền Tổng công ty HCM cấp tiền thanh toán Điện MTMN T05-2026 Đợt 2 </t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>3951311154</v>
+        <v>3451399200</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Lương bs Quý 2/2026 đợt 1 BC + Lương bs Quý 2/2026 đợt 1 CL + Lương bs Quý 2/2026 đợt 1 GD + Lương bs Quý 2/2026 đợt 1 LDCT + Lương bs Quý 2/2026 đợt 1 DVDL + Lương bs Quý 2/2026 đợt 1 APD + Lương bs Quý 2/2026 đợt 1 SG + Lương bs Quý 2/2026 đợt 1 BD + Lương bs Quý 2/2026 đợt 1 BP + Lương bs Quý 2/2026 đợt 1 CC + Lương bs Quý 2/2026 đợt 1 TND + Lương bs Quý 2/2026 đợt 1 KH + Lương bs Quý 2/2026 đợt 1 CNTT + Lương bs Quý 2/2026 đợt 1 DD + Lương bs Quý 2/2026 đợt 1 TD + Lương bs Quý 2/2026 đợt 1 VT + Lương bs Quý 2/2026 đợt 1 TA + Lương bs Quý 2/2026 đợt 1 DDO + Lương bs Quý 2/2026 đợt 1 HM + Lương bs Quý 2/2026 đợt 1 BCA + Lương bs Quý 2/2026 đợt 1 TT</t>
+          <t>Lương kỳ 1 T07/2026 LDCT + Lương kỳ 1 T07/2026 DVDL + Lương kỳ 1 T07/2026 KH + Lương kỳ 1 T07/2026 SG + Lương kỳ 1 T07/2026 CC + Lương kỳ 1 T07/2026 BC + Lương kỳ 1 T07/2026 TND + Lương kỳ 1 T07/2026 CNTT + Lương kỳ 1 T07/2026 BP + Lương kỳ 1 T07/2026 HM + Lương kỳ 1 T07/2026 DDO + Lương kỳ 1 T07/2026 APD + Lương kỳ 1 T07/2026 CL + Lương kỳ 1 T07/2026 TT + Lương kỳ 1 T07/2026 BCA + Lương kỳ 1 T07/2026 VT + Lương kỳ 1 T07/2026 DD + Lương kỳ 1 T07/2026 BD + Lương kỳ 1 T07/2026 TD + Lương kỳ 1 T07/2026 TA + Lương kỳ 1 T07/2026 GD</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Điều chỉnh hạch toán TK1131 theo G0726SC0110-10/7/26 cấp tiền lương bổ sung Q2/26 đợt 1 từ Tổng công ty</t>
+          <t>Nhập tiền cấp lương kỳ 1 T7/26 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>6973534340</v>
+        <v>18062167524</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>Cấp ĐMT T05/2026 d2 TT2248-17/6/2026</t>
+          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhập tiền Tổng công ty HCM cấp tiền thanh toán Điện MTMN T05-2026 Đợt 2 </t>
+          <t>Nhập tiền Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2471,16 +2471,16 @@
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>3451399200</v>
+        <v>3589537560</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Lương kỳ 1 T07/2026 LDCT + Lương kỳ 1 T07/2026 DVDL + Lương kỳ 1 T07/2026 KH + Lương kỳ 1 T07/2026 SG + Lương kỳ 1 T07/2026 CC + Lương kỳ 1 T07/2026 BC + Lương kỳ 1 T07/2026 TND + Lương kỳ 1 T07/2026 CNTT + Lương kỳ 1 T07/2026 BP + Lương kỳ 1 T07/2026 HM + Lương kỳ 1 T07/2026 DDO + Lương kỳ 1 T07/2026 APD + Lương kỳ 1 T07/2026 CL + Lương kỳ 1 T07/2026 TT + Lương kỳ 1 T07/2026 BCA + Lương kỳ 1 T07/2026 VT + Lương kỳ 1 T07/2026 DD + Lương kỳ 1 T07/2026 BD + Lương kỳ 1 T07/2026 TD + Lương kỳ 1 T07/2026 TA + Lương kỳ 1 T07/2026 GD</t>
+          <t>Lương kỳ 2 T07/2026 GD + Lương kỳ 2 T07/2026 BC + Lương kỳ 2 T07/2026 HM + Lương kỳ 2 T07/2026 CC + Lương kỳ 2 T07/2026 VT + Lương kỳ 2 T07/2026 DDO + Lương kỳ 2 T07/2026 DVDL + Lương kỳ 2 T07/2026 BP + Lương kỳ 2 T07/2026 LDCT + Lương kỳ 2 T07/2026 SG + Lương kỳ 2 T07/2026 BD + Lương kỳ 2 T07/2026 TA + Lương kỳ 2 T07/2026 DD + Lương kỳ 2 T07/2026 TT + Lương kỳ 2 T07/2026 TD + Lương kỳ 2 T07/2026 CNTT + Lương kỳ 2 T07/2026 APD + Lương kỳ 2 T07/2026 BCA + Lương kỳ 2 T07/2026 KH + Lương kỳ 2 T07/2026 CL + Lương kỳ 2 T07/2026 TND</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền cấp lương kỳ 1 T7/26 từ Tổng công ty</t>
+          <t>Nhập tiền cấp lương kỳ 2 T7/26 từ Tổng công ty</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -2504,16 +2504,16 @@
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>18062167524</v>
+        <v>-100891088370</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
+          <t>_KC thuế bù trừ thuế GTGT điện tháng 6.2026 với thuế GTGT ra</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
+          <t>HT bù trừ tiền thuế GTGT T06/2026</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2537,16 +2537,16 @@
         </is>
       </c>
       <c r="E26" s="16" t="n">
-        <v>3589537560</v>
+        <v>47879803</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Lương kỳ 2 T07/2026 GD + Lương kỳ 2 T07/2026 BC + Lương kỳ 2 T07/2026 HM + Lương kỳ 2 T07/2026 CC + Lương kỳ 2 T07/2026 VT + Lương kỳ 2 T07/2026 DDO + Lương kỳ 2 T07/2026 DVDL + Lương kỳ 2 T07/2026 BP + Lương kỳ 2 T07/2026 LDCT + Lương kỳ 2 T07/2026 SG + Lương kỳ 2 T07/2026 BD + Lương kỳ 2 T07/2026 TA + Lương kỳ 2 T07/2026 DD + Lương kỳ 2 T07/2026 TT + Lương kỳ 2 T07/2026 TD + Lương kỳ 2 T07/2026 CNTT + Lương kỳ 2 T07/2026 APD + Lương kỳ 2 T07/2026 BCA + Lương kỳ 2 T07/2026 KH + Lương kỳ 2 T07/2026 CL + Lương kỳ 2 T07/2026 TND</t>
+          <t>Cấp vốn SXKD (lãi vay) theo TTr 2676/TCKT ngày 09/7/26</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền cấp lương kỳ 2 T7/26 từ Tổng công ty</t>
+          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay Agribank</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -2570,16 +2570,16 @@
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-100891088370</v>
+        <v>6277098679</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>_KC thuế bù trừ thuế GTGT điện tháng 6.2026 với thuế GTGT ra</t>
+          <t>Cấp vốn SXKD thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán nợ gốc theo TTr 2839/TCKT ngày 16/7/26</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>HT bù trừ tiền thuế GTGT T06/2026</t>
+          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay SXKD</t>
         </is>
       </c>
     </row>
@@ -2589,30 +2589,30 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363611</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363611</t>
         </is>
       </c>
       <c r="E28" s="16" t="n">
-        <v>47879803</v>
+        <v>1937832476</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>Cấp vốn SXKD (lãi vay) theo TTr 2676/TCKT ngày 09/7/26</t>
+          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay Agribank</t>
+          <t>Nhập tiền thuế GTGT Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
         </is>
       </c>
     </row>
@@ -2622,30 +2622,30 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363611</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363611</t>
         </is>
       </c>
       <c r="E29" s="16" t="n">
-        <v>6277098679</v>
+        <v>-2076322697</v>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>Cấp vốn SXKD thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán lãi vay SXKD theo TTr 2839/TCKT ngày 16/7/26 + Cấp vốn KHCB thanh toán nợ gốc theo TTr 2839/TCKT ngày 16/7/26</t>
+          <t>KC thuế GTGT cấp tạm ứng T6.2026 sang công nợ thuế GTGT điện</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo sô 4084/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB trả lãi vay SXKD</t>
+          <t>Kết chuyển tiền thuế GTGT Điện NLMT T05-2026</t>
         </is>
       </c>
     </row>
@@ -2655,30 +2655,30 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>1363611</t>
+          <t>1363613</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>3363611</t>
+          <t>3363613</t>
         </is>
       </c>
       <c r="E30" s="16" t="n">
-        <v>1937832476</v>
+        <v>22176000</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Cấp DMT T06/2026 TT2746-13/7/2026 + Cấp Thuế GTGT DMT T06/2026 TT2746-13/7/2026</t>
+          <t>Cấp KHCB theo TTr 2418/TCKT ngày 24/6/2026 + Cấp thuế GTGT theo TTr 2418/TCKT ngày 24/6/2026</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>Nhập tiền thuế GTGT Tổng công ty cấp tiền Điện MTMN T06.2026 Đợt 1</t>
+          <t>Hạch toán thông báo số 4169/EVNHCMC ngày 29/7/26 cấp vốn KHCB thanh toán VAT CP vận chuyển cáp CT25038</t>
         </is>
       </c>
     </row>
@@ -2688,30 +2688,30 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>1363611</t>
+          <t>1363613</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>3363611</t>
+          <t>3363613</t>
         </is>
       </c>
       <c r="E31" s="16" t="n">
-        <v>-2076322697</v>
+        <v>7392000</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>KC thuế GTGT cấp tạm ứng T6.2026 sang công nợ thuế GTGT điện</t>
+          <t>Cấp thuế GTGT theo TTr 2796/TCKT ngày 14/7/2026 + Cấp KHCB theo TTr 2796/TCKT ngày 14/7/2026</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển tiền thuế GTGT Điện NLMT T05-2026</t>
+          <t>Hạch toán thông báo 4087/25.07.26 cấp vốn KHCB thanh toán VAT hóa đơn 6602/24.06.26 CP vận chuyển cáp CT25038</t>
         </is>
       </c>
     </row>
@@ -2721,30 +2721,30 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>1363613</t>
+          <t>13638221</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>3363613</t>
+          <t>33638221</t>
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>22176000</v>
+        <v>5650687</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>Cấp KHCB theo TTr 2418/TCKT ngày 24/6/2026 + Cấp thuế GTGT theo TTr 2418/TCKT ngày 24/6/2026</t>
+          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo số 4169/EVNHCMC ngày 29/7/26 cấp vốn KHCB thanh toán VAT CP vận chuyển cáp CT25038</t>
+          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Vi phạm HĐ điện</t>
         </is>
       </c>
     </row>
@@ -2754,30 +2754,30 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>1363613</t>
+          <t>1363843</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>3363613</t>
+          <t>3363843</t>
         </is>
       </c>
       <c r="E33" s="16" t="n">
-        <v>7392000</v>
+        <v>12789477</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>Cấp thuế GTGT theo TTr 2796/TCKT ngày 14/7/2026 + Cấp KHCB theo TTr 2796/TCKT ngày 14/7/2026</t>
+          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo 4087/25.07.26 cấp vốn KHCB thanh toán VAT hóa đơn 6602/24.06.26 CP vận chuyển cáp CT25038</t>
+          <t>Kết chuyển lợi nhuận hoạt động SXK, KD khác tháng 07/2026</t>
         </is>
       </c>
     </row>
@@ -2787,30 +2787,30 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>1363613</t>
+          <t>1363847</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>3363613</t>
+          <t>3363847</t>
         </is>
       </c>
       <c r="E34" s="16" t="n">
-        <v>849600</v>
+        <v>6574975</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>Cấp thuế GTGT theo TTr 2923/TCKT ngày 22/7/26 + Cấp KHCB theo TTr 2923/TCKT ngày 22/7/26</t>
+          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán thông báo 4089/TB-EVNHCMC ngày 25/07/26 cấp vốn KHCB thanh toán VAT HĐ 187/23.06.26 PC Bến Cát  điều chuyển VTTB cho CT25039</t>
+          <t>Kết chuyển lợi nhuận hoạt động tài chính tháng 07/2026</t>
         </is>
       </c>
     </row>
@@ -2825,16 +2825,16 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>13638221</t>
+          <t>1363848</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>33638221</t>
+          <t>3363848</t>
         </is>
       </c>
       <c r="E35" s="16" t="n">
-        <v>5650687</v>
+        <v>-2514378</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Vi phạm HĐ điện</t>
+          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - KHTSCĐ</t>
         </is>
       </c>
     </row>
@@ -2858,16 +2858,16 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>1363843</t>
+          <t>1363848</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>3363843</t>
+          <t>3363848</t>
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>12789477</v>
+        <v>31649</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận hoạt động SXK, KD khác tháng 07/2026</t>
+          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Thu dư, thu khác</t>
         </is>
       </c>
     </row>
@@ -2886,30 +2886,30 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>1363847</t>
+          <t>1363888</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>3363847</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>6574975</v>
+        <v>-9455518323</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
+          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 1853 cuả UBND Phường Phú Mỹ</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển lợi nhuận hoạt động tài chính tháng 07/2026</t>
+          <t>PCVT chuyển tiền công trình"Mở rộng, di dời lưới điện THT đường PMỹ-Tóc Tiên khu TĐC 105Ha đến đường Hắc Dịch-Tóc Tiên, Châu Pha (Quyết định 1853/QĐ-UBND ngày 29/06/26)"</t>
         </is>
       </c>
     </row>
@@ -2919,199 +2919,229 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>1363888</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>33688</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>-365738924</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 2829-17/7/2026 của UBND Phường Phú Mỹ</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Chuyển tiền về TCT công trình"DD hệ thống lưới điện trung, hạ thế thuộc dự án đường quy hoạch D22 KDC 3B đô thị mới PMỹ" (Quyết định 2829/17.07.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>2. DANH SÁCH BÚT TOÁN KHUYẾT BỊ LỆCH THEO TỪNG CẶP TÀI KHOẢN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TK HCM</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>TK PCVT</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Số Tiền Lệch Cặp</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Đơn Vị Khuyết</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Ngày CT</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Số CT GL</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Số Tiền Bút Toán</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Diễn Giải Bút Toán</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Người Lập</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>1363111</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>3363111</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>-1372690826013</v>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>1363848</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>3363848</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>-2514378</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - KHTSCĐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>8121</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>86064000</v>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>KC thuế GTGT điều động tháng 7/2026 sang công nợ thuế GTGT điện</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIENDP.HCM.NG </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>1363111</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>3363111</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>-1372690826013</v>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>1363848</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>3363848</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>31649</v>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>PNGA_4212_T07.2026 - PC Vũng Tàu</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>Kết chuyển lợi nhuận thu nhập khác tháng 07/2026 - Thu dư, thu khác</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>1363888</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>33688</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>-9455518323</v>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 1853 cuả UBND Phường Phú Mỹ</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>PCVT chuyển tiền công trình"Mở rộng, di dời lưới điện THT đường PMỹ-Tóc Tiên khu TĐC 105Ha đến đường Hắc Dịch-Tóc Tiên, Châu Pha (Quyết định 1853/QĐ-UBND ngày 29/06/26)"</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>1363888</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>33688</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>-365738924</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>Nhận tiền di dời từ PC Vũng Tàu theo QĐ 2829-17/7/2026 của UBND Phường Phú Mỹ</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>Chuyển tiền về TCT công trình"DD hệ thống lưới điện trung, hạ thế thuộc dự án đường quy hoạch D22 KDC 3B đô thị mới PMỹ" (Quyết định 2829/17.07.26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>2. DANH SÁCH BÚT TOÁN KHUYẾT BỊ LỆCH THEO TỪNG CẶP TÀI KHOẢN</t>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>2392</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>1370572291416</v>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>K/c 51111 &gt; 3363111 (k/c doanh thu điện)</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>TK HCM</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>TK PCVT</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Số Tiền Lệch Cặp</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Đơn Vị Khuyết</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Ngày CT</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Số CT GL</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Số Tiền Bút Toán</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Diễn Giải Bút Toán</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Người Lập</t>
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>1363111</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>3363111</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>-1372690826013</v>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>2159</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>2118534597</v>
+      </c>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>1363111</t>
+          <t>1363112</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>3363111</t>
+          <t>3363112</t>
         </is>
       </c>
       <c r="C46" s="16" t="n">
-        <v>-1372690826013</v>
+        <v>-715006423</v>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
@@ -3125,15 +3155,15 @@
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="G46" s="18" t="n">
-        <v>1370572291416</v>
+        <v>715006423</v>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>K/c 51111 &gt; 3363111 (k/c doanh thu điện)</t>
+          <t>K/c 51113 &gt; 3363112 (k/c dthu công suất phản kháng)</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
@@ -3145,20 +3175,20 @@
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>1363111</t>
+          <t>136314</t>
         </is>
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>3363111</t>
+          <t>336314</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>-1372690826013</v>
+        <v>-2400368334</v>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
@@ -3168,36 +3198,36 @@
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>2118534597</v>
+        <v>-2146794974</v>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
+          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
+          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>1363112</t>
+          <t>136314</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>3363112</t>
+          <t>336314</t>
         </is>
       </c>
       <c r="C48" s="16" t="n">
-        <v>-715006423</v>
+        <v>-2400368334</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
@@ -3211,15 +3241,15 @@
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="G48" s="18" t="n">
-        <v>715006423</v>
+        <v>253573360</v>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>K/c 51113 &gt; 3363112 (k/c dthu công suất phản kháng)</t>
+          <t>K/c 5114 (QL dây, cáp) &gt; 3363114</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
@@ -3231,16 +3261,16 @@
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>136314</t>
+          <t>136331</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>336314</t>
+          <t>336331</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>-2400368334</v>
+        <v>12540094089</v>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
@@ -3249,68 +3279,68 @@
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>-2146794974</v>
+        <v>2699427234</v>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
+          <t>Cấp KHCB theo TTr 2407/TCKT ngày 24/6/2026</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
+          <t xml:space="preserve">VANL.HCM.NG </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>136314</t>
+          <t>136331</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>336314</t>
+          <t>336331</t>
         </is>
       </c>
       <c r="C50" s="16" t="n">
-        <v>-2400368334</v>
+        <v>12540094089</v>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="G50" s="18" t="n">
-        <v>253573360</v>
+        <v>10620000</v>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>K/c 5114 (QL dây, cáp) &gt; 3363114</t>
+          <t>Cấp thuế GTGT theo TTr 2923/TCKT ngày 22/7/26 + Cấp KHCB theo TTr 2923/TCKT ngày 22/7/26</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
+          <t xml:space="preserve">VANL.HCM.NG </t>
         </is>
       </c>
     </row>
@@ -3631,7 +3661,7 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
@@ -3641,20 +3671,20 @@
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="G58" s="18" t="n">
-        <v>1320517500</v>
+        <v>-44500540533</v>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 TNĐL -&gt; VT</t>
+          <t>Kết chuyển công nợ nội bộ tháng 07/2026</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAM7NH.HCM.NG </t>
+          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -3674,7 +3704,7 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
@@ -3684,20 +3714,20 @@
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>729000000</v>
+        <v>-2180703957</v>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 CNTT -&gt; VT</t>
+          <t>Kết chuyển TK635111 về TCT qua TK công nợ 336358 tháng 7/2026</t>
         </is>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAM7NH.HCM.NG </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -3717,7 +3747,7 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
@@ -3727,20 +3757,20 @@
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>1075800000</v>
+        <v>12540094089</v>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 DVĐL -&gt; VT</t>
+          <t>Hạch toán món HCMC chuyển tiền cho SPC để hoàn trả tiền SPC vay</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAM7NH.HCM.NG </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -3760,7 +3790,7 @@
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
@@ -3770,36 +3800,36 @@
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-4274472878</v>
+        <v>-1235577272474</v>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>VTDD T7/2026 VT (SXKD)</t>
+          <t>HT bù trừ chi phí điện mua nội bộ trong tháng</t>
         </is>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAM7NH.HCM.NG </t>
+          <t xml:space="preserve">TUAN2HM.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363611</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363611</t>
         </is>
       </c>
       <c r="C62" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2118534597</v>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
@@ -3813,79 +3843,79 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-44500540533</v>
+        <v>-2118534597</v>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển công nợ nội bộ tháng 07/2026</t>
+          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUYENTT.HCM.VTA </t>
+          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363613</t>
         </is>
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363613</t>
         </is>
       </c>
       <c r="C63" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2366815</v>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>-2180703957</v>
+        <v>849600</v>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển TK635111 về TCT qua TK công nợ 336358 tháng 7/2026</t>
+          <t>Cấp thuế GTGT theo TTr 2923/TCKT ngày 22/7/26 + Cấp KHCB theo TTr 2923/TCKT ngày 22/7/26</t>
         </is>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">VANL.HCM.NG </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>1363613</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>3363613</t>
         </is>
       </c>
       <c r="C64" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2366815</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
@@ -3894,45 +3924,45 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>12540094089</v>
+        <v>-2366815</v>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán món HCMC chuyển tiền cho SPC để hoàn trả tiền SPC vay</t>
+          <t>Chuyển tiền thuế GTGT đã cấp về HCMC CT23009</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>136391</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>336391</t>
         </is>
       </c>
       <c r="C65" s="16" t="n">
-        <v>1269718422875</v>
+        <v>2146794974</v>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
@@ -3942,36 +3972,36 @@
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>-6773</v>
+        <v>2146794974</v>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>Xuất điều động VTTB cho Cty Thí Nghiệm Điện lực theo TB số: 3999/TB-EVNHCMC ngày 22/07/2026</t>
+          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
         </is>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C66" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
@@ -3980,41 +4010,41 @@
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>-22</v>
+        <v>-265009971</v>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>Xuất TI hạ thế Qua Đội TH2 Cty Thí Nghiệm</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23009</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C67" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
@@ -4023,41 +4053,41 @@
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-237878</v>
+        <v>-178745132</v>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>Xuất TI hạ thế Qua Đội TH2 Cty Thí Nghiệm</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23018</t>
         </is>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C68" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
@@ -4066,41 +4096,41 @@
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>-650855</v>
+        <v>-312155008</v>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>Xuất TI hạ thế Qua Đội TH2 Cty Thí Nghiệm</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21002</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C69" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
@@ -4109,41 +4139,41 @@
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>-744887</v>
+        <v>-308130</v>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>Xuất TI hạ thế Qua Đội TH2 Cty Thí Nghiệm</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho ĐVTC đền tiền Vật tư A cấp - CT23009</t>
         </is>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C70" s="16" t="n">
-        <v>1269718422875</v>
+        <v>-633614163</v>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
@@ -4152,41 +4182,41 @@
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>-1235577272474</v>
+        <v>-603285984</v>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>HT bù trừ chi phí điện mua nội bộ trong tháng</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21017</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TUAN2HM.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>1363611</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>3363611</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>2118534597</v>
+        <v>-633614163</v>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
@@ -4195,41 +4225,41 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>-2118534597</v>
+        <v>-1016165</v>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>Kết chuyển tiền thuế GTGT Điện NLMT T03-2026</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho, ĐVTC đền tiền Vật tư A cấp CT21002</t>
         </is>
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THAOPTT.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>1363613</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>3363613</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C72" s="16" t="n">
-        <v>2366815</v>
+        <v>-633614163</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
@@ -4247,59 +4277,59 @@
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-2366815</v>
+        <v>-31039400</v>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>Chuyển tiền thuế GTGT đã cấp về HCMC CT23009</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23009</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>136391</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>336391</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>2146794974</v>
+        <v>-633614163</v>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>2146794974</v>
+        <v>-48568000</v>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>Hạch toán kết chuyển DT-CP DTT năm 2025_VT</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP thiết bị điều chuyển từ SXKD CT21002</t>
         </is>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHUONGNL.HCM.NG </t>
+          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4333,11 +4363,11 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-265009971</v>
+        <v>-18000000</v>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23009</t>
+          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23018</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
@@ -4376,16 +4406,16 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-178745132</v>
+        <v>-125371702</v>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP QLDA - CT23018</t>
+          <t>Thanh toán chi phí CT22033</t>
         </is>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4419,16 +4449,16 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-312155008</v>
+        <v>-289871682</v>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21002</t>
+          <t>Thanh toán chi phí CT23007</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4462,16 +4492,16 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-308130</v>
+        <v>-275458537</v>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho ĐVTC đền tiền Vật tư A cấp - CT23009</t>
+          <t>Thanh toán chi phí CT21007</t>
         </is>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4505,16 +4535,16 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-603285984</v>
+        <v>-848733059</v>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CPQLDA CT21017</t>
+          <t>Thanh toán chi phí CT20009</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4548,16 +4578,16 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>-1016165</v>
+        <v>-240595694</v>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP bảo hiểm lưu kho, ĐVTC đền tiền Vật tư A cấp CT21002</t>
+          <t>Thanh toán chi phí CT24006</t>
         </is>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4591,16 +4621,16 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>-31039400</v>
+        <v>-155287323</v>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23009</t>
+          <t>Thanh toán chi phí CT21055</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4625,25 +4655,25 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>-48568000</v>
+        <v>292565243</v>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP thiết bị điều chuyển từ SXKD CT21002</t>
+          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4668,25 +4698,25 @@
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>-18000000</v>
+        <v>-24025976</v>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tất toán CP CT ĐTXD - CP vận chuyển - CT23018</t>
+          <t>25039-SX:Xuất Vtư từ Ctr Trang TBị đóng cắt Scada đ/c trả lại kho SXKD do cấp thừa</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4711,25 +4741,25 @@
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>-284000000</v>
+        <v>14264000</v>
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tiền VTTB điều chuyển từ SXKD qua các CT ĐTXD CT26004</t>
+          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4754,25 +4784,25 @@
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>-2415427234</v>
+        <v>119133842</v>
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán tiền VTTB điều chuyển từ SXKD qua các CT ĐTXD CT25006</t>
+          <t>SXKD-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINH3NTT.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4797,25 +4827,25 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>-125371702</v>
+        <v>12303466</v>
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán chi phí CT22033</t>
+          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
         </is>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4840,25 +4870,25 @@
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>-289871682</v>
+        <v>-104673235</v>
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán chi phí CT23007</t>
+          <t>25017-SX:Xuất Vtư thừa từ Ctr 25017-Lộ ra Côn Đảo điều chuyển SXKD phục vụ SCTX</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4883,25 +4913,25 @@
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>-275458537</v>
+        <v>91276000</v>
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán chi phí CT21007</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4926,25 +4956,25 @@
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>-848733059</v>
+        <v>41322000</v>
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán chi phí CT20009</t>
+          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển cho Ctr 25018-Tụ bù trung thế 2025</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -4969,25 +4999,25 @@
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>-240595694</v>
+        <v>-267630000</v>
       </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán chi phí CT24006</t>
+          <t>24027-SX:Xuất Vtư từ Ctr 24027- CQT Tx.Phú Mỹ để điều chuyển qua SXKD</t>
         </is>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -5012,25 +5042,25 @@
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>-155287323</v>
+        <v>95719600</v>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>Thanh toán chi phí CT21055</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039- Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
+          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -5055,20 +5085,20 @@
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>292565243</v>
+        <v>51954506</v>
       </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
@@ -5098,20 +5128,20 @@
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>-24025976</v>
+        <v>13378750</v>
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>25039-SX:Xuất Vtư từ Ctr Trang TBị đóng cắt Scada đ/c trả lại kho SXKD do cấp thừa</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -5141,20 +5171,20 @@
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>14264000</v>
+        <v>-817800</v>
       </c>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>SX-25039: Nhập Vtư từ SXKD điều chuyển qua Ctr 25039-Trang TBị đóng cắt Scada</t>
+          <t>24029-SX:Xuất Vtư Ctr 24029-Lộ ra Tân Phước đ/chuyển SXKD phục vụ SCTX</t>
         </is>
       </c>
       <c r="I93" s="15" t="inlineStr">
@@ -5184,20 +5214,20 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>119133842</v>
+        <v>12799411</v>
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>SXKD-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
+          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển qua Ctr 25039- Trang TBị đóng cắt Scada</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -5227,25 +5257,25 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>12303466</v>
+        <v>7962963</v>
       </c>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển qua Ctr 25018-Tụ bù trung thế 2025</t>
+          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 440/21.07.26</t>
         </is>
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -5270,25 +5300,25 @@
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>-104673235</v>
+        <v>8473850</v>
       </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>25017-SX:Xuất Vtư thừa từ Ctr 25017-Lộ ra Côn Đảo điều chuyển SXKD phục vụ SCTX</t>
+          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 600/29.07.26</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
+          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>
       </c>
     </row>
@@ -5313,496 +5343,23 @@
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>91276000</v>
+        <v>4619000</v>
       </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr Ctr 25039-Trang TBị đóng cắt Scada</t>
+          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 2161/30.07.26</t>
         </is>
       </c>
       <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C98" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F98" s="15" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G98" s="18" t="n">
-        <v>41322000</v>
-      </c>
-      <c r="H98" s="17" t="inlineStr">
-        <is>
-          <t>SX-25018:Nhập Vtư từ SXKD điều chuyển cho Ctr 25018-Tụ bù trung thế 2025</t>
-        </is>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F99" s="15" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G99" s="18" t="n">
-        <v>-267630000</v>
-      </c>
-      <c r="H99" s="17" t="inlineStr">
-        <is>
-          <t>24027-SX:Xuất Vtư từ Ctr 24027- CQT Tx.Phú Mỹ để điều chuyển qua SXKD</t>
-        </is>
-      </c>
-      <c r="I99" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F100" s="15" t="inlineStr">
-        <is>
-          <t>2139</t>
-        </is>
-      </c>
-      <c r="G100" s="18" t="n">
-        <v>95719600</v>
-      </c>
-      <c r="H100" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039- Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F101" s="15" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="G101" s="18" t="n">
-        <v>51954506</v>
-      </c>
-      <c r="H101" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B102" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F102" s="15" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="G102" s="18" t="n">
-        <v>13378750</v>
-      </c>
-      <c r="H102" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển cho Ctr 25039-Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I102" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E103" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="F103" s="15" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="G103" s="18" t="n">
-        <v>-817800</v>
-      </c>
-      <c r="H103" s="17" t="inlineStr">
-        <is>
-          <t>24029-SX:Xuất Vtư Ctr 24029-Lộ ra Tân Phước đ/chuyển SXKD phục vụ SCTX</t>
-        </is>
-      </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="F104" s="15" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="G104" s="18" t="n">
-        <v>12799411</v>
-      </c>
-      <c r="H104" s="17" t="inlineStr">
-        <is>
-          <t>SX-25039:Nhập Vtư từ SXKD điều chuyển qua Ctr 25039- Trang TBị đóng cắt Scada</t>
-        </is>
-      </c>
-      <c r="I104" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THANH5DT.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B105" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F105" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G105" s="18" t="n">
-        <v>46285000</v>
-      </c>
-      <c r="H105" s="17" t="inlineStr">
-        <is>
-          <t>Xuất VTTB  03.VH1.51.0024 /15.06.26 về ĐTXD (Máy tính xách tay _Nguyễn Văn Quyến +Thước đo lăn+Thước đo bằng tia Laser cho P.QLĐT)</t>
-        </is>
-      </c>
-      <c r="I105" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F106" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G106" s="18" t="n">
-        <v>7962963</v>
-      </c>
-      <c r="H106" s="17" t="inlineStr">
-        <is>
-          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 440/21.07.26</t>
-        </is>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E107" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F107" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G107" s="18" t="n">
-        <v>8473850</v>
-      </c>
-      <c r="H107" s="17" t="inlineStr">
-        <is>
-          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 600/29.07.26</t>
-        </is>
-      </c>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIENNTK.HCM.VTA </t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="inlineStr">
-        <is>
-          <t>33681</t>
-        </is>
-      </c>
-      <c r="C108" s="16" t="n">
-        <v>-633614163</v>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="F108" s="15" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="G108" s="18" t="n">
-        <v>4619000</v>
-      </c>
-      <c r="H108" s="17" t="inlineStr">
-        <is>
-          <t>Chi phí đặt ăn công tác ĐTXD_Hóa đơn 2161/30.07.26</t>
-        </is>
-      </c>
-      <c r="I108" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">HIENNTK.HCM.VTA </t>
         </is>

--- a/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
+++ b/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>PCVT</t>
+          <t>Điện lực</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>TK PCVT</t>
+          <t>TK Điện lực</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Diễn Giải (PCVT)</t>
+          <t>Diễn Giải (Điện lực)</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>TK PCVT</t>
+          <t>TK Điện lực</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại HCM (Khuyết PCVT)</t>
+          <t>Chỉ có tại HCM (Khuyết Điện lực)</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E93" s="15" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E95" s="15" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>Chỉ có tại PCVT (Khuyết HCM)</t>
+          <t>Chỉ có tại Điện lực (Khuyết HCM)</t>
         </is>
       </c>
       <c r="E97" s="15" t="inlineStr">

--- a/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
+++ b/đầu ra/Bao_Cao_Doi_Soat_136_336_Thang_7_2026.xlsx
@@ -1947,7 +1947,7 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>🏢 Bút Toán Điện Lực Bị Thiếu (1 chứng từ)</t>
+          <t>🏢 Bút Toán Điện Lực Bị Thiếu (0 chứng từ)</t>
         </is>
       </c>
     </row>
@@ -2014,24 +2014,14 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>8121</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>86064000</v>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>KC thuế GTGT điều động tháng 7/2026 sang công nợ thuế GTGT điện</t>
-        </is>
-      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>✅ Phía Điện lực đã hạch toán đầy đủ.</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -4372,83 +4362,84 @@
       <c r="E170" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="A25:I25"/>
+  <mergeCells count="77">
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F117:I117"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="A94:I95"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A84:I85"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A5:I6"/>
+    <mergeCell ref="F97:I97"/>
+    <mergeCell ref="A134:I135"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="F107:I107"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A114:I115"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="A60:I61"/>
+    <mergeCell ref="A16:I17"/>
+    <mergeCell ref="A93:I93"/>
+    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A124:I125"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A137:D137"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="F109:I109"/>
+    <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A46:I46"/>
     <mergeCell ref="A133:I133"/>
     <mergeCell ref="F39:I39"/>
     <mergeCell ref="A109:D109"/>
-    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A63:D63"/>
-    <mergeCell ref="F117:I117"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="F107:I107"/>
     <mergeCell ref="A113:I113"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A114:I115"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A48:I49"/>
     <mergeCell ref="F87:I87"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="A94:I95"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F137:I137"/>
+    <mergeCell ref="F89:I89"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="F139:I139"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A71:I72"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A132:I132"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A47:I47"/>
     <mergeCell ref="A122:I122"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="A84:I85"/>
-    <mergeCell ref="A107:D107"/>
-    <mergeCell ref="A60:I61"/>
-    <mergeCell ref="F137:I137"/>
     <mergeCell ref="A36:I37"/>
-    <mergeCell ref="A16:I17"/>
-    <mergeCell ref="F89:I89"/>
     <mergeCell ref="A112:I112"/>
     <mergeCell ref="F127:I127"/>
     <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A93:I93"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A124:I125"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="F139:I139"/>
     <mergeCell ref="F21:I21"/>
-    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A71:I72"/>
-    <mergeCell ref="A34:I34"/>
     <mergeCell ref="F51:I51"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A137:D137"/>
-    <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A26:I27"/>
     <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A59:I59"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A103:I103"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="A5:I6"/>
-    <mergeCell ref="F97:I97"/>
-    <mergeCell ref="F109:I109"/>
-    <mergeCell ref="A123:I123"/>
     <mergeCell ref="F129:I129"/>
-    <mergeCell ref="A132:I132"/>
     <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A134:I135"/>
     <mergeCell ref="A104:I105"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A69:I69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
